--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130822178</v>
       </c>
       <c r="B2" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130822165</v>
+        <v>130822176</v>
       </c>
       <c r="B3" t="n">
-        <v>57863</v>
+        <v>91772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423776</v>
+        <v>423906</v>
       </c>
       <c r="R3" t="n">
-        <v>7049067</v>
+        <v>7049117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130822176</v>
+        <v>130822165</v>
       </c>
       <c r="B4" t="n">
-        <v>91771</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423906</v>
+        <v>423776</v>
       </c>
       <c r="R4" t="n">
-        <v>7049117</v>
+        <v>7049067</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>130823164</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130822161</v>
+        <v>130822157</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423797</v>
+        <v>423796</v>
       </c>
       <c r="R6" t="n">
-        <v>7049125</v>
+        <v>7049158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130822157</v>
+        <v>130822161</v>
       </c>
       <c r="B7" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423796</v>
+        <v>423797</v>
       </c>
       <c r="R7" t="n">
-        <v>7049158</v>
+        <v>7049125</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,7 +1309,7 @@
         <v>130823162</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>130823161</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130823155</v>
+        <v>130823153</v>
       </c>
       <c r="B10" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>423787</v>
+        <v>423817</v>
       </c>
       <c r="R10" t="n">
-        <v>7049107</v>
+        <v>7049177</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, längs några meter på en granstam. I flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,6 +1666,11 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1703,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130823153</v>
+        <v>130823155</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>423817</v>
+        <v>423787</v>
       </c>
       <c r="R11" t="n">
-        <v>7049177</v>
+        <v>7049107</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1791,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en granstam. I flerskiktad granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,11 +1806,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130823151</v>
+        <v>130823163</v>
       </c>
       <c r="B12" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,31 +1854,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>423970</v>
+        <v>423854</v>
       </c>
       <c r="R12" t="n">
-        <v>7049090</v>
+        <v>7049136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,6 +1930,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1955,12 +1951,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1978,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130823163</v>
+        <v>130823151</v>
       </c>
       <c r="B13" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,26 +1985,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2016,10 +2017,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>423854</v>
+        <v>423970</v>
       </c>
       <c r="R13" t="n">
-        <v>7049136</v>
+        <v>7049090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2056,7 +2057,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,7 +2066,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
         <v>130823159</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>130823154</v>
       </c>
       <c r="B15" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>130823160</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>130822162</v>
       </c>
       <c r="B17" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>130823157</v>
       </c>
       <c r="B18" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130823156</v>
+        <v>130822180</v>
       </c>
       <c r="B19" t="n">
-        <v>57863</v>
+        <v>91772</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,42 +2754,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>423747</v>
+        <v>423732</v>
       </c>
       <c r="R19" t="n">
-        <v>7049131</v>
+        <v>7049150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2824,11 +2816,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2837,51 +2824,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130822180</v>
+        <v>130822182</v>
       </c>
       <c r="B20" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2913,10 +2875,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423732</v>
+        <v>423748</v>
       </c>
       <c r="R20" t="n">
-        <v>7049150</v>
+        <v>7049159</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2975,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130822182</v>
+        <v>130823158</v>
       </c>
       <c r="B21" t="n">
-        <v>91771</v>
+        <v>91796</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,34 +2948,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423748</v>
+        <v>423730</v>
       </c>
       <c r="R21" t="n">
-        <v>7049159</v>
+        <v>7049088</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3048,34 +3009,65 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130823158</v>
+        <v>130823169</v>
       </c>
       <c r="B22" t="n">
-        <v>91795</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,19 +3075,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -3106,10 +3102,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423730</v>
+        <v>423752</v>
       </c>
       <c r="R22" t="n">
-        <v>7049088</v>
+        <v>7049166</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3146,7 +3142,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3176,12 +3172,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3199,10 +3195,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130823169</v>
+        <v>130823156</v>
       </c>
       <c r="B23" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,26 +3206,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3237,10 +3238,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423752</v>
+        <v>423747</v>
       </c>
       <c r="R23" t="n">
-        <v>7049166</v>
+        <v>7049131</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3277,7 +3278,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3286,7 +3287,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130822170</v>
+        <v>130823150</v>
       </c>
       <c r="B24" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,16 +3359,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>423780</v>
+        <v>423989</v>
       </c>
       <c r="R24" t="n">
-        <v>7049026</v>
+        <v>7049100</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3405,7 +3413,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3416,26 +3424,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130823150</v>
+        <v>130822170</v>
       </c>
       <c r="B25" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,24 +3494,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>423989</v>
+        <v>423780</v>
       </c>
       <c r="R25" t="n">
-        <v>7049100</v>
+        <v>7049026</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3515,7 +3540,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3526,41 +3551,16 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
         <v>130822163</v>
       </c>
       <c r="B26" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130822155</v>
+        <v>130822160</v>
       </c>
       <c r="B27" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424042</v>
+        <v>423800</v>
       </c>
       <c r="R27" t="n">
-        <v>7049125</v>
+        <v>7049140</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130822172</v>
+        <v>130822155</v>
       </c>
       <c r="B28" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>423678</v>
+        <v>424042</v>
       </c>
       <c r="R28" t="n">
-        <v>7048965</v>
+        <v>7049125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3873,10 +3873,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130822160</v>
+        <v>130822172</v>
       </c>
       <c r="B29" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>423800</v>
+        <v>423678</v>
       </c>
       <c r="R29" t="n">
-        <v>7049140</v>
+        <v>7048965</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
         <v>130823168</v>
       </c>
       <c r="B30" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>130823167</v>
       </c>
       <c r="B31" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4237,10 +4237,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130822159</v>
+        <v>130822154</v>
       </c>
       <c r="B32" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>423805</v>
+        <v>423964</v>
       </c>
       <c r="R32" t="n">
-        <v>7049145</v>
+        <v>7049137</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130822158</v>
+        <v>130823152</v>
       </c>
       <c r="B33" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4368,16 +4368,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>423797</v>
+        <v>423916</v>
       </c>
       <c r="R33" t="n">
-        <v>7049151</v>
+        <v>7049107</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4414,7 +4422,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4425,26 +4433,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130822154</v>
+        <v>130822158</v>
       </c>
       <c r="B34" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4476,10 +4509,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>423964</v>
+        <v>423797</v>
       </c>
       <c r="R34" t="n">
-        <v>7049137</v>
+        <v>7049151</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4543,10 +4576,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130823152</v>
+        <v>130822159</v>
       </c>
       <c r="B35" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4572,24 +4605,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>423916</v>
+        <v>423805</v>
       </c>
       <c r="R35" t="n">
-        <v>7049107</v>
+        <v>7049145</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4626,7 +4651,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4637,41 +4662,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4681,7 +4681,7 @@
         <v>130822153</v>
       </c>
       <c r="B36" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>130822164</v>
       </c>
       <c r="B37" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -2743,10 +2743,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130822180</v>
+        <v>130823156</v>
       </c>
       <c r="B19" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,34 +2754,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>423732</v>
+        <v>423747</v>
       </c>
       <c r="R19" t="n">
-        <v>7049150</v>
+        <v>7049131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2816,6 +2824,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2824,23 +2837,48 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130822182</v>
+        <v>130822180</v>
       </c>
       <c r="B20" t="n">
         <v>91772</v>
@@ -2875,10 +2913,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423748</v>
+        <v>423732</v>
       </c>
       <c r="R20" t="n">
-        <v>7049159</v>
+        <v>7049150</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2937,10 +2975,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130823158</v>
+        <v>130822182</v>
       </c>
       <c r="B21" t="n">
-        <v>91796</v>
+        <v>91772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,33 +2986,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423730</v>
+        <v>423748</v>
       </c>
       <c r="R21" t="n">
-        <v>7049088</v>
+        <v>7049159</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3009,65 +3048,34 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130823169</v>
+        <v>130823158</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3075,23 +3083,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -3102,10 +3106,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423752</v>
+        <v>423730</v>
       </c>
       <c r="R22" t="n">
-        <v>7049166</v>
+        <v>7049088</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3142,7 +3146,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,12 +3176,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3195,10 +3199,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130823156</v>
+        <v>130823169</v>
       </c>
       <c r="B23" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3206,31 +3210,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3238,10 +3237,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423747</v>
+        <v>423752</v>
       </c>
       <c r="R23" t="n">
-        <v>7049131</v>
+        <v>7049166</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3278,7 +3277,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3287,6 +3286,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130822176</v>
+        <v>130822165</v>
       </c>
       <c r="B3" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423906</v>
+        <v>423776</v>
       </c>
       <c r="R3" t="n">
-        <v>7049117</v>
+        <v>7049067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130822165</v>
+        <v>130822176</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423776</v>
+        <v>423906</v>
       </c>
       <c r="R4" t="n">
-        <v>7049067</v>
+        <v>7049117</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2506,7 +2506,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130822162</v>
+        <v>130823157</v>
       </c>
       <c r="B17" t="n">
         <v>57864</v>
@@ -2535,16 +2535,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>423784</v>
+        <v>423749</v>
       </c>
       <c r="R17" t="n">
-        <v>7049096</v>
+        <v>7049126</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2581,7 +2589,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2592,23 +2600,48 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130823157</v>
+        <v>130822162</v>
       </c>
       <c r="B18" t="n">
         <v>57864</v>
@@ -2637,24 +2670,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>423749</v>
+        <v>423784</v>
       </c>
       <c r="R18" t="n">
-        <v>7049126</v>
+        <v>7049096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2691,7 +2716,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2702,41 +2727,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130822180</v>
+        <v>130823158</v>
       </c>
       <c r="B20" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2889,34 +2889,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423732</v>
+        <v>423730</v>
       </c>
       <c r="R20" t="n">
-        <v>7049150</v>
+        <v>7049088</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2951,31 +2950,62 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130822182</v>
+        <v>130822180</v>
       </c>
       <c r="B21" t="n">
         <v>91772</v>
@@ -3010,10 +3040,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423748</v>
+        <v>423732</v>
       </c>
       <c r="R21" t="n">
-        <v>7049159</v>
+        <v>7049150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3072,10 +3102,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130823158</v>
+        <v>130822182</v>
       </c>
       <c r="B22" t="n">
-        <v>91796</v>
+        <v>91772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,33 +3113,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423730</v>
+        <v>423748</v>
       </c>
       <c r="R22" t="n">
-        <v>7049088</v>
+        <v>7049159</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3144,55 +3175,24 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3567,7 +3567,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130822163</v>
+        <v>130822155</v>
       </c>
       <c r="B26" t="n">
         <v>57864</v>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>423782</v>
+        <v>424042</v>
       </c>
       <c r="R26" t="n">
-        <v>7049081</v>
+        <v>7049125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3669,7 +3669,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130822160</v>
+        <v>130822163</v>
       </c>
       <c r="B27" t="n">
         <v>57864</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>423800</v>
+        <v>423782</v>
       </c>
       <c r="R27" t="n">
-        <v>7049140</v>
+        <v>7049081</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3771,7 +3771,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130822155</v>
+        <v>130822160</v>
       </c>
       <c r="B28" t="n">
         <v>57864</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424042</v>
+        <v>423800</v>
       </c>
       <c r="R28" t="n">
-        <v>7049125</v>
+        <v>7049140</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130823167</v>
+        <v>130822158</v>
       </c>
       <c r="B31" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,37 +4117,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>423730</v>
+        <v>423797</v>
       </c>
       <c r="R31" t="n">
-        <v>7049099</v>
+        <v>7049151</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4184,7 +4181,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4193,44 +4190,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4339,10 +4310,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130823152</v>
+        <v>130823167</v>
       </c>
       <c r="B33" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4350,31 +4321,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4382,10 +4348,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>423916</v>
+        <v>423730</v>
       </c>
       <c r="R33" t="n">
-        <v>7049107</v>
+        <v>7049099</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4422,7 +4388,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4431,6 +4397,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4451,12 +4418,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4474,7 +4441,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130822158</v>
+        <v>130822159</v>
       </c>
       <c r="B34" t="n">
         <v>57864</v>
@@ -4509,10 +4476,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>423797</v>
+        <v>423805</v>
       </c>
       <c r="R34" t="n">
-        <v>7049151</v>
+        <v>7049145</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4549,7 +4516,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4576,7 +4543,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130822159</v>
+        <v>130823152</v>
       </c>
       <c r="B35" t="n">
         <v>57864</v>
@@ -4605,16 +4572,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>423805</v>
+        <v>423916</v>
       </c>
       <c r="R35" t="n">
-        <v>7049145</v>
+        <v>7049107</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4651,7 +4626,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4662,16 +4637,41 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130822165</v>
+        <v>130822176</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423776</v>
+        <v>423906</v>
       </c>
       <c r="R3" t="n">
-        <v>7049067</v>
+        <v>7049117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130822176</v>
+        <v>130822165</v>
       </c>
       <c r="B4" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423906</v>
+        <v>423776</v>
       </c>
       <c r="R4" t="n">
-        <v>7049117</v>
+        <v>7049067</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2506,7 +2506,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130823157</v>
+        <v>130822162</v>
       </c>
       <c r="B17" t="n">
         <v>57864</v>
@@ -2535,24 +2535,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>423749</v>
+        <v>423784</v>
       </c>
       <c r="R17" t="n">
-        <v>7049126</v>
+        <v>7049096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2589,7 +2581,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2600,48 +2592,23 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130822162</v>
+        <v>130823157</v>
       </c>
       <c r="B18" t="n">
         <v>57864</v>
@@ -2670,16 +2637,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>423784</v>
+        <v>423749</v>
       </c>
       <c r="R18" t="n">
-        <v>7049096</v>
+        <v>7049126</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2716,7 +2691,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2727,26 +2702,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130823156</v>
+        <v>130823169</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,31 +2754,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2786,10 +2781,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>423747</v>
+        <v>423752</v>
       </c>
       <c r="R19" t="n">
-        <v>7049131</v>
+        <v>7049166</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2826,7 +2821,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2835,6 +2830,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2855,12 +2851,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2878,10 +2874,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130823158</v>
+        <v>130823156</v>
       </c>
       <c r="B20" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2889,22 +2885,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2912,10 +2917,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423730</v>
+        <v>423747</v>
       </c>
       <c r="R20" t="n">
-        <v>7049088</v>
+        <v>7049131</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2952,7 +2957,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
+          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2961,7 +2966,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2982,12 +2986,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3005,10 +3009,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130822180</v>
+        <v>130823158</v>
       </c>
       <c r="B21" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,34 +3020,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423732</v>
+        <v>423730</v>
       </c>
       <c r="R21" t="n">
-        <v>7049150</v>
+        <v>7049088</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3078,31 +3081,62 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130822182</v>
+        <v>130822180</v>
       </c>
       <c r="B22" t="n">
         <v>91772</v>
@@ -3137,10 +3171,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423748</v>
+        <v>423732</v>
       </c>
       <c r="R22" t="n">
-        <v>7049159</v>
+        <v>7049150</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3199,10 +3233,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130823169</v>
+        <v>130822182</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>91772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,37 +3244,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423752</v>
+        <v>423748</v>
       </c>
       <c r="R23" t="n">
-        <v>7049166</v>
+        <v>7049159</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3275,55 +3306,24 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -2240,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130823154</v>
+        <v>130823160</v>
       </c>
       <c r="B15" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,31 +2251,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>423791</v>
+        <v>423881</v>
       </c>
       <c r="R15" t="n">
-        <v>7049103</v>
+        <v>7049037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2323,7 +2318,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,6 +2327,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2352,12 +2348,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2375,10 +2371,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130823160</v>
+        <v>130823154</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,26 +2382,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2413,10 +2414,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>423881</v>
+        <v>423791</v>
       </c>
       <c r="R16" t="n">
-        <v>7049037</v>
+        <v>7049103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2453,7 +2454,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,7 +2463,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130823156</v>
+        <v>130822180</v>
       </c>
       <c r="B20" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,42 +2885,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423747</v>
+        <v>423732</v>
       </c>
       <c r="R20" t="n">
-        <v>7049131</v>
+        <v>7049150</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2955,11 +2947,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2968,41 +2955,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3136,7 +3098,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130822180</v>
+        <v>130822182</v>
       </c>
       <c r="B22" t="n">
         <v>91772</v>
@@ -3171,10 +3133,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423732</v>
+        <v>423748</v>
       </c>
       <c r="R22" t="n">
-        <v>7049150</v>
+        <v>7049159</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3233,10 +3195,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130822182</v>
+        <v>130823156</v>
       </c>
       <c r="B23" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,34 +3206,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423748</v>
+        <v>423747</v>
       </c>
       <c r="R23" t="n">
-        <v>7049159</v>
+        <v>7049131</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3306,6 +3276,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3314,16 +3289,41 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3567,7 +3567,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130822155</v>
+        <v>130822163</v>
       </c>
       <c r="B26" t="n">
         <v>57864</v>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424042</v>
+        <v>423782</v>
       </c>
       <c r="R26" t="n">
-        <v>7049125</v>
+        <v>7049081</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3669,7 +3669,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130822163</v>
+        <v>130822160</v>
       </c>
       <c r="B27" t="n">
         <v>57864</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>423782</v>
+        <v>423800</v>
       </c>
       <c r="R27" t="n">
-        <v>7049081</v>
+        <v>7049140</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3771,7 +3771,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130822160</v>
+        <v>130822155</v>
       </c>
       <c r="B28" t="n">
         <v>57864</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>423800</v>
+        <v>424042</v>
       </c>
       <c r="R28" t="n">
-        <v>7049140</v>
+        <v>7049125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130822158</v>
+        <v>130823167</v>
       </c>
       <c r="B31" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,34 +4117,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>423797</v>
+        <v>423730</v>
       </c>
       <c r="R31" t="n">
-        <v>7049151</v>
+        <v>7049099</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4181,7 +4184,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4190,18 +4193,44 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4310,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130823167</v>
+        <v>130823152</v>
       </c>
       <c r="B33" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4321,26 +4350,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4348,10 +4382,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>423730</v>
+        <v>423916</v>
       </c>
       <c r="R33" t="n">
-        <v>7049099</v>
+        <v>7049107</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4388,7 +4422,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
+          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4397,7 +4431,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4418,12 +4451,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4441,7 +4474,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130822159</v>
+        <v>130822158</v>
       </c>
       <c r="B34" t="n">
         <v>57864</v>
@@ -4476,10 +4509,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>423805</v>
+        <v>423797</v>
       </c>
       <c r="R34" t="n">
-        <v>7049145</v>
+        <v>7049151</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4516,7 +4549,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4543,7 +4576,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130823152</v>
+        <v>130822159</v>
       </c>
       <c r="B35" t="n">
         <v>57864</v>
@@ -4572,24 +4605,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>423916</v>
+        <v>423805</v>
       </c>
       <c r="R35" t="n">
-        <v>7049107</v>
+        <v>7049145</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4626,7 +4651,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4637,41 +4662,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130822176</v>
+        <v>130822165</v>
       </c>
       <c r="B3" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423906</v>
+        <v>423776</v>
       </c>
       <c r="R3" t="n">
-        <v>7049117</v>
+        <v>7049067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130822165</v>
+        <v>130822176</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423776</v>
+        <v>423906</v>
       </c>
       <c r="R4" t="n">
-        <v>7049067</v>
+        <v>7049117</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130823164</v>
+        <v>130822157</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,37 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423807</v>
+        <v>423796</v>
       </c>
       <c r="R5" t="n">
-        <v>7049107</v>
+        <v>7049158</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1058,51 +1055,25 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130822157</v>
+        <v>130822161</v>
       </c>
       <c r="B6" t="n">
         <v>57864</v>
@@ -1137,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423796</v>
+        <v>423797</v>
       </c>
       <c r="R6" t="n">
-        <v>7049158</v>
+        <v>7049125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1148,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130822161</v>
+        <v>130823164</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1186,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423797</v>
+        <v>423807</v>
       </c>
       <c r="R7" t="n">
-        <v>7049125</v>
+        <v>7049107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,7 +1253,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Relativt rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1288,18 +1262,44 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130823163</v>
+        <v>130823151</v>
       </c>
       <c r="B12" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,26 +1854,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>423854</v>
+        <v>423970</v>
       </c>
       <c r="R12" t="n">
-        <v>7049136</v>
+        <v>7049090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,7 +1935,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1951,12 +1955,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1974,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130823151</v>
+        <v>130823163</v>
       </c>
       <c r="B13" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,31 +1989,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2017,10 +2016,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>423970</v>
+        <v>423854</v>
       </c>
       <c r="R13" t="n">
-        <v>7049090</v>
+        <v>7049136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,7 +2056,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,6 +2065,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130823160</v>
+        <v>130823154</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,26 +2251,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>423881</v>
+        <v>423791</v>
       </c>
       <c r="R15" t="n">
-        <v>7049037</v>
+        <v>7049103</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,7 +2323,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,7 +2332,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2348,12 +2352,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2371,10 +2375,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130823154</v>
+        <v>130823160</v>
       </c>
       <c r="B16" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,31 +2386,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2414,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>423791</v>
+        <v>423881</v>
       </c>
       <c r="R16" t="n">
-        <v>7049103</v>
+        <v>7049037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2454,7 +2453,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,6 +2462,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130823169</v>
+        <v>130823158</v>
       </c>
       <c r="B19" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,23 +2754,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -2781,10 +2777,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>423752</v>
+        <v>423730</v>
       </c>
       <c r="R19" t="n">
-        <v>7049166</v>
+        <v>7049088</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2821,7 +2817,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,12 +2847,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2874,10 +2870,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130822180</v>
+        <v>130823156</v>
       </c>
       <c r="B20" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,34 +2881,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423732</v>
+        <v>423747</v>
       </c>
       <c r="R20" t="n">
-        <v>7049150</v>
+        <v>7049131</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2947,6 +2951,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2955,26 +2964,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130823158</v>
+        <v>130823169</v>
       </c>
       <c r="B21" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,19 +3016,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -3005,10 +3043,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423730</v>
+        <v>423752</v>
       </c>
       <c r="R21" t="n">
-        <v>7049088</v>
+        <v>7049166</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3045,7 +3083,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,12 +3113,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3098,7 +3136,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130822182</v>
+        <v>130822180</v>
       </c>
       <c r="B22" t="n">
         <v>91772</v>
@@ -3133,10 +3171,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423748</v>
+        <v>423732</v>
       </c>
       <c r="R22" t="n">
-        <v>7049159</v>
+        <v>7049150</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3195,10 +3233,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130823156</v>
+        <v>130822182</v>
       </c>
       <c r="B23" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3206,42 +3244,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423747</v>
+        <v>423748</v>
       </c>
       <c r="R23" t="n">
-        <v>7049131</v>
+        <v>7049159</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3276,11 +3306,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3289,41 +3314,16 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130823167</v>
+        <v>130822154</v>
       </c>
       <c r="B31" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,37 +4117,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>423730</v>
+        <v>423964</v>
       </c>
       <c r="R31" t="n">
-        <v>7049099</v>
+        <v>7049137</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4184,7 +4181,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4193,51 +4190,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130822154</v>
+        <v>130823152</v>
       </c>
       <c r="B32" t="n">
         <v>57864</v>
@@ -4266,16 +4237,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>423964</v>
+        <v>423916</v>
       </c>
       <c r="R32" t="n">
-        <v>7049137</v>
+        <v>7049107</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4312,7 +4291,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4323,23 +4302,48 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130823152</v>
+        <v>130822158</v>
       </c>
       <c r="B33" t="n">
         <v>57864</v>
@@ -4368,24 +4372,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>423916</v>
+        <v>423797</v>
       </c>
       <c r="R33" t="n">
-        <v>7049107</v>
+        <v>7049151</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4422,7 +4418,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4433,48 +4429,23 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130822158</v>
+        <v>130822159</v>
       </c>
       <c r="B34" t="n">
         <v>57864</v>
@@ -4509,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>423797</v>
+        <v>423805</v>
       </c>
       <c r="R34" t="n">
-        <v>7049151</v>
+        <v>7049145</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4549,7 +4520,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4576,10 +4547,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130822159</v>
+        <v>130823167</v>
       </c>
       <c r="B35" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4587,34 +4558,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>423805</v>
+        <v>423730</v>
       </c>
       <c r="R35" t="n">
-        <v>7049145</v>
+        <v>7049099</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4651,7 +4625,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4660,18 +4634,44 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130822178</v>
       </c>
       <c r="B2" t="n">
-        <v>91772</v>
+        <v>91780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130822165</v>
+        <v>130822176</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>91780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423776</v>
+        <v>423906</v>
       </c>
       <c r="R3" t="n">
-        <v>7049067</v>
+        <v>7049117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130822176</v>
+        <v>130822165</v>
       </c>
       <c r="B4" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423906</v>
+        <v>423776</v>
       </c>
       <c r="R4" t="n">
-        <v>7049117</v>
+        <v>7049067</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130822157</v>
+        <v>130823164</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,34 +982,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423796</v>
+        <v>423807</v>
       </c>
       <c r="R5" t="n">
-        <v>7049158</v>
+        <v>7049107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1049,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Relativt rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1055,25 +1058,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130822161</v>
+        <v>130822157</v>
       </c>
       <c r="B6" t="n">
         <v>57864</v>
@@ -1108,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423797</v>
+        <v>423796</v>
       </c>
       <c r="R6" t="n">
-        <v>7049125</v>
+        <v>7049158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,7 +1177,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130823164</v>
+        <v>130822161</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,37 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423807</v>
+        <v>423797</v>
       </c>
       <c r="R7" t="n">
-        <v>7049107</v>
+        <v>7049125</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,7 +1279,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,44 +1288,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130823151</v>
+        <v>130823163</v>
       </c>
       <c r="B12" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,31 +1854,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>423970</v>
+        <v>423854</v>
       </c>
       <c r="R12" t="n">
-        <v>7049090</v>
+        <v>7049136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,6 +1930,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1955,12 +1951,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1978,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130823163</v>
+        <v>130823151</v>
       </c>
       <c r="B13" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,26 +1985,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2016,10 +2017,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>423854</v>
+        <v>423970</v>
       </c>
       <c r="R13" t="n">
-        <v>7049136</v>
+        <v>7049090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2056,7 +2057,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,7 +2066,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130823154</v>
+        <v>130823160</v>
       </c>
       <c r="B15" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,31 +2251,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>423791</v>
+        <v>423881</v>
       </c>
       <c r="R15" t="n">
-        <v>7049103</v>
+        <v>7049037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2323,7 +2318,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,6 +2327,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2352,12 +2348,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2375,10 +2371,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130823160</v>
+        <v>130823154</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,26 +2382,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2413,10 +2414,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>423881</v>
+        <v>423791</v>
       </c>
       <c r="R16" t="n">
-        <v>7049037</v>
+        <v>7049103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2453,7 +2454,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,7 +2463,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130823158</v>
+        <v>130822180</v>
       </c>
       <c r="B19" t="n">
-        <v>91796</v>
+        <v>91780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,33 +2754,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>423730</v>
+        <v>423732</v>
       </c>
       <c r="R19" t="n">
-        <v>7049088</v>
+        <v>7049150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2815,65 +2816,34 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130823156</v>
+        <v>130822182</v>
       </c>
       <c r="B20" t="n">
-        <v>57864</v>
+        <v>91780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2881,42 +2851,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423747</v>
+        <v>423748</v>
       </c>
       <c r="R20" t="n">
-        <v>7049131</v>
+        <v>7049159</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2951,11 +2913,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2964,51 +2921,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130823169</v>
+        <v>130823158</v>
       </c>
       <c r="B21" t="n">
-        <v>79221</v>
+        <v>91804</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,23 +2948,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -3043,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423752</v>
+        <v>423730</v>
       </c>
       <c r="R21" t="n">
-        <v>7049166</v>
+        <v>7049088</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3083,7 +3011,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3113,12 +3041,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3136,10 +3064,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130822180</v>
+        <v>130823169</v>
       </c>
       <c r="B22" t="n">
-        <v>91772</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3147,34 +3075,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423732</v>
+        <v>423752</v>
       </c>
       <c r="R22" t="n">
-        <v>7049150</v>
+        <v>7049166</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3209,34 +3140,65 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hyfsad mängd bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130822182</v>
+        <v>130823156</v>
       </c>
       <c r="B23" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,34 +3206,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423748</v>
+        <v>423747</v>
       </c>
       <c r="R23" t="n">
-        <v>7049159</v>
+        <v>7049131</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3306,6 +3276,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3314,16 +3289,41 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3567,7 +3567,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130822163</v>
+        <v>130822155</v>
       </c>
       <c r="B26" t="n">
         <v>57864</v>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>423782</v>
+        <v>424042</v>
       </c>
       <c r="R26" t="n">
-        <v>7049081</v>
+        <v>7049125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3669,7 +3669,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130822160</v>
+        <v>130822163</v>
       </c>
       <c r="B27" t="n">
         <v>57864</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>423800</v>
+        <v>423782</v>
       </c>
       <c r="R27" t="n">
-        <v>7049140</v>
+        <v>7049081</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3771,7 +3771,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130822155</v>
+        <v>130822160</v>
       </c>
       <c r="B28" t="n">
         <v>57864</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424042</v>
+        <v>423800</v>
       </c>
       <c r="R28" t="n">
-        <v>7049125</v>
+        <v>7049140</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130822154</v>
+        <v>130823167</v>
       </c>
       <c r="B31" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,34 +4117,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>423964</v>
+        <v>423730</v>
       </c>
       <c r="R31" t="n">
-        <v>7049137</v>
+        <v>7049099</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4181,7 +4184,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4190,25 +4193,51 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130823152</v>
+        <v>130822154</v>
       </c>
       <c r="B32" t="n">
         <v>57864</v>
@@ -4237,24 +4266,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>423916</v>
+        <v>423964</v>
       </c>
       <c r="R32" t="n">
-        <v>7049107</v>
+        <v>7049137</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4291,7 +4312,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4302,48 +4323,23 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130822158</v>
+        <v>130823152</v>
       </c>
       <c r="B33" t="n">
         <v>57864</v>
@@ -4372,16 +4368,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>423797</v>
+        <v>423916</v>
       </c>
       <c r="R33" t="n">
-        <v>7049151</v>
+        <v>7049107</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4418,7 +4422,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4429,23 +4433,48 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130822159</v>
+        <v>130822158</v>
       </c>
       <c r="B34" t="n">
         <v>57864</v>
@@ -4480,10 +4509,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>423805</v>
+        <v>423797</v>
       </c>
       <c r="R34" t="n">
-        <v>7049145</v>
+        <v>7049151</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4520,7 +4549,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4547,10 +4576,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130823167</v>
+        <v>130822159</v>
       </c>
       <c r="B35" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,37 +4587,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>423730</v>
+        <v>423805</v>
       </c>
       <c r="R35" t="n">
-        <v>7049099</v>
+        <v>7049145</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4625,7 +4651,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4634,44 +4660,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130822157</v>
+        <v>130822161</v>
       </c>
       <c r="B6" t="n">
         <v>57864</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423796</v>
+        <v>423797</v>
       </c>
       <c r="R6" t="n">
-        <v>7049158</v>
+        <v>7049125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130822161</v>
+        <v>130822157</v>
       </c>
       <c r="B7" t="n">
         <v>57864</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423797</v>
+        <v>423796</v>
       </c>
       <c r="R7" t="n">
-        <v>7049125</v>
+        <v>7049158</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1568,7 +1568,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130823153</v>
+        <v>130823155</v>
       </c>
       <c r="B10" t="n">
         <v>57864</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>423817</v>
+        <v>423787</v>
       </c>
       <c r="R10" t="n">
-        <v>7049177</v>
+        <v>7049107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en granstam. I flerskiktad granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,11 +1666,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1708,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130823155</v>
+        <v>130823153</v>
       </c>
       <c r="B11" t="n">
         <v>57864</v>
@@ -1751,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>423787</v>
+        <v>423817</v>
       </c>
       <c r="R11" t="n">
-        <v>7049107</v>
+        <v>7049177</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1786,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, längs några meter på en granstam. I flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,6 +1801,11 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2240,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130823160</v>
+        <v>130823154</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,26 +2251,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>423881</v>
+        <v>423791</v>
       </c>
       <c r="R15" t="n">
-        <v>7049037</v>
+        <v>7049103</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,7 +2323,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,7 +2332,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2348,12 +2352,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2371,10 +2375,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130823154</v>
+        <v>130823160</v>
       </c>
       <c r="B16" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,31 +2386,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2414,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>423791</v>
+        <v>423881</v>
       </c>
       <c r="R16" t="n">
-        <v>7049103</v>
+        <v>7049037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2454,7 +2453,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,6 +2462,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130822180</v>
+        <v>130823156</v>
       </c>
       <c r="B19" t="n">
-        <v>91780</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,34 +2754,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>423732</v>
+        <v>423747</v>
       </c>
       <c r="R19" t="n">
-        <v>7049150</v>
+        <v>7049131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2816,6 +2824,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2824,23 +2837,48 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130822182</v>
+        <v>130822180</v>
       </c>
       <c r="B20" t="n">
         <v>91780</v>
@@ -2875,10 +2913,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423748</v>
+        <v>423732</v>
       </c>
       <c r="R20" t="n">
-        <v>7049159</v>
+        <v>7049150</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2937,10 +2975,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130823158</v>
+        <v>130822182</v>
       </c>
       <c r="B21" t="n">
-        <v>91804</v>
+        <v>91780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,33 +2986,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423730</v>
+        <v>423748</v>
       </c>
       <c r="R21" t="n">
-        <v>7049088</v>
+        <v>7049159</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3009,65 +3048,34 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130823169</v>
+        <v>130823158</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>91804</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3075,23 +3083,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -3102,10 +3106,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423752</v>
+        <v>423730</v>
       </c>
       <c r="R22" t="n">
-        <v>7049166</v>
+        <v>7049088</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3142,7 +3146,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,12 +3176,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3195,10 +3199,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130823156</v>
+        <v>130823169</v>
       </c>
       <c r="B23" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3206,31 +3210,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3238,10 +3237,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423747</v>
+        <v>423752</v>
       </c>
       <c r="R23" t="n">
-        <v>7049131</v>
+        <v>7049166</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3278,7 +3277,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3287,6 +3286,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130823150</v>
+        <v>130822170</v>
       </c>
       <c r="B24" t="n">
         <v>57864</v>
@@ -3359,24 +3359,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>423989</v>
+        <v>423780</v>
       </c>
       <c r="R24" t="n">
-        <v>7049100</v>
+        <v>7049026</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3413,7 +3405,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3424,48 +3416,23 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130822170</v>
+        <v>130823150</v>
       </c>
       <c r="B25" t="n">
         <v>57864</v>
@@ -3494,16 +3461,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>423780</v>
+        <v>423989</v>
       </c>
       <c r="R25" t="n">
-        <v>7049026</v>
+        <v>7049100</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3540,7 +3515,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3551,23 +3526,48 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130822155</v>
+        <v>130822163</v>
       </c>
       <c r="B26" t="n">
         <v>57864</v>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424042</v>
+        <v>423782</v>
       </c>
       <c r="R26" t="n">
-        <v>7049125</v>
+        <v>7049081</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3669,7 +3669,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130822163</v>
+        <v>130822155</v>
       </c>
       <c r="B27" t="n">
         <v>57864</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>423782</v>
+        <v>424042</v>
       </c>
       <c r="R27" t="n">
-        <v>7049081</v>
+        <v>7049125</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3771,7 +3771,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130822160</v>
+        <v>130822172</v>
       </c>
       <c r="B28" t="n">
         <v>57864</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>423800</v>
+        <v>423678</v>
       </c>
       <c r="R28" t="n">
-        <v>7049140</v>
+        <v>7048965</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130822172</v>
+        <v>130822160</v>
       </c>
       <c r="B29" t="n">
         <v>57864</v>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>423678</v>
+        <v>423800</v>
       </c>
       <c r="R29" t="n">
-        <v>7048965</v>
+        <v>7049140</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130822154</v>
+        <v>130822159</v>
       </c>
       <c r="B32" t="n">
         <v>57864</v>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>423964</v>
+        <v>423805</v>
       </c>
       <c r="R32" t="n">
-        <v>7049137</v>
+        <v>7049145</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4339,7 +4339,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130823152</v>
+        <v>130822158</v>
       </c>
       <c r="B33" t="n">
         <v>57864</v>
@@ -4368,24 +4368,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>423916</v>
+        <v>423797</v>
       </c>
       <c r="R33" t="n">
-        <v>7049107</v>
+        <v>7049151</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4422,7 +4414,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4433,48 +4425,23 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130822158</v>
+        <v>130822154</v>
       </c>
       <c r="B34" t="n">
         <v>57864</v>
@@ -4509,10 +4476,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>423797</v>
+        <v>423964</v>
       </c>
       <c r="R34" t="n">
-        <v>7049151</v>
+        <v>7049137</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4576,7 +4543,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130822159</v>
+        <v>130823152</v>
       </c>
       <c r="B35" t="n">
         <v>57864</v>
@@ -4605,16 +4572,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>423805</v>
+        <v>423916</v>
       </c>
       <c r="R35" t="n">
-        <v>7049145</v>
+        <v>7049107</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4651,7 +4626,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4662,16 +4637,41 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130822178</v>
       </c>
       <c r="B2" t="n">
-        <v>91780</v>
+        <v>91794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130822176</v>
+        <v>130822165</v>
       </c>
       <c r="B3" t="n">
-        <v>91780</v>
+        <v>57878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423906</v>
+        <v>423776</v>
       </c>
       <c r="R3" t="n">
-        <v>7049117</v>
+        <v>7049067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130822165</v>
+        <v>130822176</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>91794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423776</v>
+        <v>423906</v>
       </c>
       <c r="R4" t="n">
-        <v>7049067</v>
+        <v>7049117</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130823164</v>
+        <v>130822161</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>57878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,37 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423807</v>
+        <v>423797</v>
       </c>
       <c r="R5" t="n">
-        <v>7049107</v>
+        <v>7049125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1058,54 +1055,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130822161</v>
+        <v>130822157</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423797</v>
+        <v>423796</v>
       </c>
       <c r="R6" t="n">
-        <v>7049125</v>
+        <v>7049158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1148,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130822157</v>
+        <v>130823164</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>79235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1186,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423796</v>
+        <v>423807</v>
       </c>
       <c r="R7" t="n">
-        <v>7049158</v>
+        <v>7049107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,7 +1253,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Relativt rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1288,18 +1262,44 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
         <v>130823162</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>130823161</v>
       </c>
       <c r="B9" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>130823155</v>
       </c>
       <c r="B10" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>130823153</v>
       </c>
       <c r="B11" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>130823163</v>
       </c>
       <c r="B12" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>130823151</v>
       </c>
       <c r="B13" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>130823159</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>130823154</v>
       </c>
       <c r="B15" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>130823160</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>130822162</v>
       </c>
       <c r="B17" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>130823157</v>
       </c>
       <c r="B18" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130823156</v>
+        <v>130822180</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>91794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,42 +2754,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>423747</v>
+        <v>423732</v>
       </c>
       <c r="R19" t="n">
-        <v>7049131</v>
+        <v>7049150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2824,11 +2816,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2837,51 +2824,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130822180</v>
+        <v>130822182</v>
       </c>
       <c r="B20" t="n">
-        <v>91780</v>
+        <v>91794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2913,10 +2875,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423732</v>
+        <v>423748</v>
       </c>
       <c r="R20" t="n">
-        <v>7049150</v>
+        <v>7049159</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2975,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130822182</v>
+        <v>130823158</v>
       </c>
       <c r="B21" t="n">
-        <v>91780</v>
+        <v>91818</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,34 +2948,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423748</v>
+        <v>423730</v>
       </c>
       <c r="R21" t="n">
-        <v>7049159</v>
+        <v>7049088</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3048,34 +3009,65 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130823158</v>
+        <v>130823169</v>
       </c>
       <c r="B22" t="n">
-        <v>91804</v>
+        <v>79235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,19 +3075,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -3106,10 +3102,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423730</v>
+        <v>423752</v>
       </c>
       <c r="R22" t="n">
-        <v>7049088</v>
+        <v>7049166</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3146,7 +3142,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3176,12 +3172,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3199,10 +3195,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130823169</v>
+        <v>130823156</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>57878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,26 +3206,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3237,10 +3238,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423752</v>
+        <v>423747</v>
       </c>
       <c r="R23" t="n">
-        <v>7049166</v>
+        <v>7049131</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3277,7 +3278,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3286,7 +3287,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130822170</v>
+        <v>130823150</v>
       </c>
       <c r="B24" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,16 +3359,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>423780</v>
+        <v>423989</v>
       </c>
       <c r="R24" t="n">
-        <v>7049026</v>
+        <v>7049100</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3405,7 +3413,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3416,26 +3424,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130823150</v>
+        <v>130822170</v>
       </c>
       <c r="B25" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,24 +3494,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>423989</v>
+        <v>423780</v>
       </c>
       <c r="R25" t="n">
-        <v>7049100</v>
+        <v>7049026</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3515,7 +3540,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3526,41 +3551,16 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
         <v>130822163</v>
       </c>
       <c r="B26" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>130822155</v>
       </c>
       <c r="B27" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130822172</v>
+        <v>130822160</v>
       </c>
       <c r="B28" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>423678</v>
+        <v>423800</v>
       </c>
       <c r="R28" t="n">
-        <v>7048965</v>
+        <v>7049140</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3873,10 +3873,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130822160</v>
+        <v>130822172</v>
       </c>
       <c r="B29" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>423800</v>
+        <v>423678</v>
       </c>
       <c r="R29" t="n">
-        <v>7049140</v>
+        <v>7048965</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
         <v>130823168</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>130823167</v>
       </c>
       <c r="B31" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>130822159</v>
       </c>
       <c r="B32" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>130822158</v>
       </c>
       <c r="B33" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>130822154</v>
       </c>
       <c r="B34" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>130823152</v>
       </c>
       <c r="B35" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>130822153</v>
       </c>
       <c r="B36" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>130822164</v>
       </c>
       <c r="B37" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130822178</v>
       </c>
       <c r="B2" t="n">
-        <v>91805</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130822176</v>
+        <v>130823167</v>
       </c>
       <c r="B3" t="n">
-        <v>91805</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423906</v>
+        <v>423730</v>
       </c>
       <c r="R3" t="n">
-        <v>7049117</v>
+        <v>7049099</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,34 +848,65 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130822165</v>
+        <v>130822172</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423776</v>
+        <v>423678</v>
       </c>
       <c r="R4" t="n">
-        <v>7049067</v>
+        <v>7048965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130822161</v>
+        <v>130822176</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423797</v>
+        <v>423906</v>
       </c>
       <c r="R5" t="n">
-        <v>7049125</v>
+        <v>7049117</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1076,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130822157</v>
+        <v>130822180</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423796</v>
+        <v>423732</v>
       </c>
       <c r="R6" t="n">
-        <v>7049158</v>
+        <v>7049150</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1173,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130823164</v>
+        <v>130822182</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,37 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423807</v>
+        <v>423748</v>
       </c>
       <c r="R7" t="n">
-        <v>7049107</v>
+        <v>7049159</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,69 +1272,38 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med garnlav på flera granar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130823162</v>
+        <v>130823159</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1344,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>423940</v>
+        <v>423864</v>
       </c>
       <c r="R8" t="n">
-        <v>7049110</v>
+        <v>7049094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,7 +1374,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer på en stående död avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,12 +1404,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1437,14 +1427,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130823161</v>
+        <v>130823160</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1475,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>423938</v>
+        <v>423881</v>
       </c>
       <c r="R9" t="n">
-        <v>7049017</v>
+        <v>7049037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1505,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På björk i flerskiktad granskog.</t>
+          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,22 +1525,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1568,42 +1558,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130823155</v>
+        <v>130823161</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1611,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>423787</v>
+        <v>423938</v>
       </c>
       <c r="R10" t="n">
-        <v>7049107</v>
+        <v>7049017</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1636,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På björk i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,6 +1645,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1670,22 +1656,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1703,42 +1689,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130823153</v>
+        <v>130823162</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1746,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>423817</v>
+        <v>423940</v>
       </c>
       <c r="R11" t="n">
-        <v>7049177</v>
+        <v>7049110</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1767,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en granstam. I flerskiktad granskog.</t>
+          <t>Växer på en stående död avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,6 +1776,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1803,11 +1785,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad skog med inslag av björk.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1820,12 +1797,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1843,42 +1820,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130823151</v>
+        <v>130823163</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1886,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>423970</v>
+        <v>423854</v>
       </c>
       <c r="R12" t="n">
-        <v>7049090</v>
+        <v>7049136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1898,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,6 +1907,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1955,12 +1928,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1978,14 +1951,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130823163</v>
+        <v>130823164</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2016,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>423854</v>
+        <v>423807</v>
       </c>
       <c r="R13" t="n">
-        <v>7049136</v>
+        <v>7049107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2056,7 +2029,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Relativt rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2109,14 +2082,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130823159</v>
+        <v>130823168</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2147,10 +2120,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>423864</v>
+        <v>423754</v>
       </c>
       <c r="R14" t="n">
-        <v>7049094</v>
+        <v>7049119</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2187,7 +2160,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Hyfsat rikligt med garnlav på flera granar i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2240,42 +2213,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130823154</v>
+        <v>130823169</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2283,10 +2251,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>423791</v>
+        <v>423752</v>
       </c>
       <c r="R15" t="n">
-        <v>7049103</v>
+        <v>7049166</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2323,7 +2291,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Hyfsad mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,6 +2300,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2352,12 +2321,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2375,10 +2344,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130823160</v>
+        <v>130822153</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,37 +2355,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>423881</v>
+        <v>423970</v>
       </c>
       <c r="R16" t="n">
-        <v>7049037</v>
+        <v>7049041</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2453,7 +2427,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en stående död avbarkad gran med full längd.</t>
+          <t>Troligt tretå-bohål ca 4 m upp i grantickerötad gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,54 +2436,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130822162</v>
+        <v>130822154</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,10 +2489,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>423784</v>
+        <v>423964</v>
       </c>
       <c r="R17" t="n">
-        <v>7049096</v>
+        <v>7049137</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2581,7 +2529,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2608,10 +2556,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130823157</v>
+        <v>130822155</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2637,24 +2585,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>423749</v>
+        <v>424042</v>
       </c>
       <c r="R18" t="n">
-        <v>7049126</v>
+        <v>7049125</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2691,7 +2631,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2702,51 +2642,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130822180</v>
+        <v>130822156</v>
       </c>
       <c r="B19" t="n">
-        <v>91805</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,21 +2669,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2778,10 +2693,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>423732</v>
+        <v>423778</v>
       </c>
       <c r="R19" t="n">
-        <v>7049150</v>
+        <v>7049190</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,6 +2729,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2840,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130822182</v>
+        <v>130822157</v>
       </c>
       <c r="B20" t="n">
-        <v>91805</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,21 +2771,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2875,10 +2795,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423748</v>
+        <v>423796</v>
       </c>
       <c r="R20" t="n">
-        <v>7049159</v>
+        <v>7049158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,6 +2831,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130823156</v>
+        <v>130822158</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2966,24 +2891,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423747</v>
+        <v>423797</v>
       </c>
       <c r="R21" t="n">
-        <v>7049131</v>
+        <v>7049151</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3020,7 +2937,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3031,51 +2948,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130823158</v>
+        <v>130822159</v>
       </c>
       <c r="B22" t="n">
-        <v>91829</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,33 +2975,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423730</v>
+        <v>423805</v>
       </c>
       <c r="R22" t="n">
-        <v>7049088</v>
+        <v>7049145</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3146,7 +3039,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Små fruktkroppar i en ca 3 meters granhögstubbe.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3155,54 +3048,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130823169</v>
+        <v>130822160</v>
       </c>
       <c r="B23" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,37 +3077,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423752</v>
+        <v>423800</v>
       </c>
       <c r="R23" t="n">
-        <v>7049166</v>
+        <v>7049140</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3277,7 +3141,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hyfsad mängd bålar på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3286,54 +3150,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130822170</v>
+        <v>130822161</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,10 +3203,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>423780</v>
+        <v>423797</v>
       </c>
       <c r="R24" t="n">
-        <v>7049026</v>
+        <v>7049125</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3405,7 +3243,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130823150</v>
+        <v>130822162</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,24 +3299,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>423989</v>
+        <v>423784</v>
       </c>
       <c r="R25" t="n">
-        <v>7049100</v>
+        <v>7049096</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3515,7 +3345,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3526,41 +3356,16 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3570,7 +3375,7 @@
         <v>130822163</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3669,10 +3474,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130822155</v>
+        <v>130822164</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,10 +3509,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424042</v>
+        <v>423779</v>
       </c>
       <c r="R27" t="n">
-        <v>7049125</v>
+        <v>7049075</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3549,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3771,10 +3576,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130822172</v>
+        <v>130822165</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3806,10 +3611,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>423678</v>
+        <v>423776</v>
       </c>
       <c r="R28" t="n">
-        <v>7048965</v>
+        <v>7049067</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3873,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130822160</v>
+        <v>130822166</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>423800</v>
+        <v>423773</v>
       </c>
       <c r="R29" t="n">
-        <v>7049140</v>
+        <v>7049054</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3948,7 +3753,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3975,10 +3780,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130823168</v>
+        <v>130822167</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3986,37 +3791,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartnäset Djupsjö, Jmt</t>
+          <t>Djupsjö ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>423754</v>
+        <v>423772</v>
       </c>
       <c r="R30" t="n">
-        <v>7049119</v>
+        <v>7049052</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4053,7 +3855,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt med garnlav på flera granar i gammal bitvis flerskiktad granskog.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4062,54 +3864,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130822159</v>
+        <v>130822170</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4141,10 +3917,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>423805</v>
+        <v>423780</v>
       </c>
       <c r="R31" t="n">
-        <v>7049145</v>
+        <v>7049026</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4181,7 +3957,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4208,10 +3984,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130822158</v>
+        <v>130823150</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4237,16 +4013,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>423797</v>
+        <v>423989</v>
       </c>
       <c r="R32" t="n">
-        <v>7049151</v>
+        <v>7049100</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4283,7 +4067,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4294,26 +4078,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130822154</v>
+        <v>130823151</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4339,16 +4148,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>423964</v>
+        <v>423970</v>
       </c>
       <c r="R33" t="n">
-        <v>7049137</v>
+        <v>7049090</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4385,7 +4202,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4396,16 +4213,41 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4415,7 +4257,7 @@
         <v>130823152</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4547,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130823167</v>
+        <v>130823153</v>
       </c>
       <c r="B35" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,26 +4400,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4585,10 +4432,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>423730</v>
+        <v>423817</v>
       </c>
       <c r="R35" t="n">
-        <v>7049099</v>
+        <v>7049177</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4625,7 +4472,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
+          <t>Ringhack, äldre, längs några meter på en granstam. I flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4634,7 +4481,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4643,6 +4489,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad skog med inslag av björk.</t>
+        </is>
+      </c>
       <c r="AJ35" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4655,12 +4506,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4678,10 +4529,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130822153</v>
+        <v>130823154</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4711,20 +4562,20 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>423970</v>
+        <v>423791</v>
       </c>
       <c r="R36" t="n">
-        <v>7049041</v>
+        <v>7049103</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4761,7 +4612,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Troligt tretå-bohål ca 4 m upp i grantickerötad gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4772,26 +4623,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130822164</v>
+        <v>130823155</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,16 +4693,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupsjö ö, Jmt</t>
+          <t>Svartnäset Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>423779</v>
+        <v>423787</v>
       </c>
       <c r="R37" t="n">
-        <v>7049075</v>
+        <v>7049107</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4863,7 +4747,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4874,19 +4758,314 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130823156</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svartnäset Djupsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>423747</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7049131</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, på gran, äldre men faller möjligen inom ramen för färska.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130823157</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svartnäset Djupsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>423749</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7049126</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62273-2025 artfynd.xlsx
+++ b/artfynd/A 62273-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822176</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822178</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822180</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822182</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823159</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823160</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823161</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823162</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1715,6 +1760,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823163</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1846,6 +1896,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823164</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1977,6 +2032,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823167</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2108,6 +2168,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823168</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2239,6 +2304,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823169</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2349,6 +2419,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822153</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2451,6 +2526,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822154</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2553,6 +2633,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822155</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2655,6 +2740,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822156</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2757,6 +2847,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822157</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2859,6 +2954,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822158</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2961,6 +3061,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822159</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3063,6 +3168,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822160</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3165,6 +3275,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822161</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3267,6 +3382,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822162</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3369,6 +3489,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822163</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3471,6 +3596,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822164</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3573,6 +3703,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822165</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3675,6 +3810,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822166</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3777,6 +3917,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822167</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3879,6 +4024,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822170</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3981,6 +4131,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822172</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4116,6 +4271,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823150</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4251,6 +4411,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823151</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4386,6 +4551,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823152</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4526,6 +4696,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823153</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4661,6 +4836,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823154</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4796,6 +4976,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823155</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4931,6 +5116,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823156</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5066,8 +5256,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130823157</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>